--- a/data/trans_orig/IP21B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Clase-trans_orig.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46047</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>52599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>22696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27449</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50325</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>87,07%</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
